--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.40360552456581</v>
+        <v>7.865585897741945</v>
       </c>
       <c r="D2" t="n">
-        <v>4.430601981627252</v>
+        <v>0.7199728220144285</v>
       </c>
       <c r="E2" t="n">
-        <v>15.00531496755363</v>
+        <v>2.438363682227465</v>
       </c>
       <c r="F2" t="n">
-        <v>17.39789047075041</v>
+        <v>2.827157201496942</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.51728240697316</v>
+        <v>3.334058391133139</v>
       </c>
       <c r="D3" t="n">
-        <v>27.97651978998621</v>
+        <v>4.54618446587276</v>
       </c>
       <c r="E3" t="n">
-        <v>15.00531496755363</v>
+        <v>2.438363682227465</v>
       </c>
       <c r="F3" t="n">
-        <v>17.39789047075041</v>
+        <v>2.827157201496942</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.78372270757508</v>
+        <v>4.027354939980951</v>
       </c>
       <c r="D4" t="n">
-        <v>26.81356547005847</v>
+        <v>4.357204388884503</v>
       </c>
       <c r="E4" t="n">
-        <v>15.00531496755363</v>
+        <v>2.438363682227465</v>
       </c>
       <c r="F4" t="n">
-        <v>17.39789047075041</v>
+        <v>2.827157201496942</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.34097179749175</v>
+        <v>5.25540791709241</v>
       </c>
       <c r="D5" t="n">
-        <v>31.16781362581546</v>
+        <v>5.064769714195012</v>
       </c>
       <c r="E5" t="n">
-        <v>15.00531496755363</v>
+        <v>2.438363682227465</v>
       </c>
       <c r="F5" t="n">
-        <v>17.39789047075041</v>
+        <v>2.827157201496942</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>60.0967820057236</v>
+        <v>9.765727075930085</v>
       </c>
       <c r="D6" t="n">
-        <v>53.20866476577049</v>
+        <v>8.646408024437704</v>
       </c>
       <c r="E6" t="n">
-        <v>15.00531496755363</v>
+        <v>2.438363682227465</v>
       </c>
       <c r="F6" t="n">
-        <v>17.39789047075041</v>
+        <v>2.827157201496942</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>54.37806242460115</v>
+        <v>8.836435143997688</v>
       </c>
       <c r="D7" t="n">
-        <v>55.91364472048559</v>
+        <v>9.085967267078908</v>
       </c>
       <c r="E7" t="n">
-        <v>15.00531496755363</v>
+        <v>2.438363682227465</v>
       </c>
       <c r="F7" t="n">
-        <v>17.39789047075041</v>
+        <v>2.827157201496942</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
